--- a/out/Attention-S4_repeat_3_000006.xlsx
+++ b/out/Attention-S4_repeat_3_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-3.03186320216187</v>
+        <v>2.305762781659078</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-3.03186320216187</v>
+        <v>2.305762781659078</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-3.03186320216187</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-3.03186320216187</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-3.03186320216187</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.4174590227899861</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.4174590227899861</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.017459022789986</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.017459022789986</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.431863202161871</v>
+        <v>2.305762781659078</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.017459022789986</v>
+        <v>2.305762781659078</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.017459022789986</v>
+        <v>2.305762781659078</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.017459022789986</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.4174590227899861</v>
+        <v>-0.4521789472830329</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.4174590227899861</v>
+        <v>-0.4521789472830329</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.4174590227899861</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.4174590227899861</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.4174590227899861</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.4174590227899861</v>
+        <v>-0.4521789472830329</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.4174590227899861</v>
+        <v>-0.4521789472830329</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.4174590227899861</v>
+        <v>2.305762781659078</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-3.03186320216187</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.4174590227899861</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.4174590227899861</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-3.03186320216187</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-3.03186320216187</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.4174590227899861</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.4174590227899861</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.017459022789986</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002167933316328563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2790299051992228</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.558587869200261</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.06443947414094801</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2143736377266419</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2143736377266419</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2143736377266419</v>
+        <v>-1.132978215301409e-05</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.03480737878934635</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-3.03186320216187</v>
+        <v>2.305762781659078</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2143736377266419</v>
+        <v>0.06967306260766974</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.006658702747694012</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.4174590227899861</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2142181103627183</v>
+        <v>0.04813339109669218</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2098254224174885</v>
+        <v>0.01166497710546563</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-3.03186320216187</v>
+        <v>-0.4521789472830329</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.6344178076558942</v>
+        <v>0.06480756565131712</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1189164494470218</v>
+        <v>0.006386101950949885</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.017459022789986</v>
+        <v>2.905762781659078</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6621722477533422</v>
+        <v>0.06590631286349753</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.04545446575991044</v>
+        <v>0.002634458308807825</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-3.03186320216187</v>
+        <v>-0.4521789472830329</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6339956083353591</v>
+        <v>0.06478416367584373</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.07232407436583781</v>
+        <v>0.003283870444541329</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.017459022789986</v>
+        <v>-0.4521789472830329</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.7332013087964265</v>
+        <v>0.06871740681828419</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04462322612253995</v>
+        <v>0.001975313973506252</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-2.431863202161871</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.7500666126926449</v>
+        <v>0.06938237945495802</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03529366886793676</v>
+        <v>0.001500557139511183</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.7760110817772639</v>
+        <v>0.07040750301207835</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01545949057915544</v>
+        <v>0.0006609133754705257</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.7716012733357656</v>
+        <v>0.07022771066259011</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01265231612104198</v>
+        <v>0.0005221422689700339</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.7814412070586635</v>
+        <v>0.07061341381629208</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.006267748663672829</v>
+        <v>0.0002576554276470299</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.7813183675816443</v>
+        <v>0.0706037260687896</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003670753839263306</v>
+        <v>0.0001462784387727361</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7823862616255859</v>
+        <v>0.07064139980206754</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001832876919631653</v>
+        <v>7.063921938636807e-05</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.7823788710057181</v>
+        <v>0.07063630562613346</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0009025361073440396</v>
+        <v>3.237042611096213e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.7823498572915786</v>
+        <v>0.07063032503723772</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0005251638152329905</v>
+        <v>1.836356944531915e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7824971497944204</v>
+        <v>0.07063178593129758</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001678093721583097</v>
+        <v>1.695910341915725e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.7823092626698283</v>
+        <v>0.07061902842826256</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>8.19713484444194e-05</v>
+        <v>-5.08417705457914e-07</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.782305295364584</v>
+        <v>0.0706140781286098</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.375480506233813e-05</v>
+        <v>-2.553803869891494e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.7823086581029661</v>
+        <v>0.07060947635424719</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.745641700775619e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.782302030110225</v>
+        <v>0.07060940024723555</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>8.923309997209489e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.7823029483463702</v>
+        <v>0.07060993991513574</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.358871600787948e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.7822959460555492</v>
+        <v>0.07060960781181254</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.16696438401113e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7822920839804529</v>
+        <v>0.07060998834687029</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.938917334575396e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7822875366682678</v>
+        <v>0.07061021666790498</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7822876266129177</v>
+        <v>0.07061030661255494</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.7822867686793329</v>
+        <v>0.07060944867897011</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.7822869970003676</v>
+        <v>0.0706096770000048</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.7822862013361559</v>
+        <v>0.07060888133579306</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.782286263605529</v>
+        <v>0.07060894360516616</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.7822862912808058</v>
+        <v>0.07060897128044302</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7822864434948291</v>
+        <v>0.0706091234944663</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.7822860975538674</v>
+        <v>0.07060877755350456</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.782286173660879</v>
+        <v>0.07060885366051621</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7822863397125406</v>
+        <v>0.0706090197121778</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.7822866994911407</v>
+        <v>0.07060937949077785</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.7822867202475984</v>
+        <v>0.07060940024723555</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.7822868240298868</v>
+        <v>0.07060950402952405</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-2.431863202161871</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7822870523509216</v>
+        <v>0.07060973235055874</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.7822869278121753</v>
+        <v>0.07060960781181254</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.7822869554874522</v>
+        <v>0.0706096354870894</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.7822870108380061</v>
+        <v>0.07060969083764335</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.7822872737531369</v>
+        <v>0.07060995375277404</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.782287190727306</v>
+        <v>0.07060987072694325</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7822869831627293</v>
+        <v>0.07060966316236648</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7822869970003676</v>
+        <v>0.0706096770000048</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7822871353767523</v>
+        <v>0.07060981537638954</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7822868517051638</v>
+        <v>0.0706095317048009</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7822866787346829</v>
+        <v>0.07060935873432016</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7822865749523945</v>
+        <v>0.07060925495203166</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.7822867202475984</v>
+        <v>0.07060940024723555</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7822869624062716</v>
+        <v>0.07060964240590879</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7822867894357907</v>
+        <v>0.0706094694354278</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.7822864919265636</v>
+        <v>0.07060917192620085</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7822864780889252</v>
+        <v>0.07060915808856232</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7822861113915059</v>
+        <v>0.07060879139114311</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.7822861113915059</v>
+        <v>0.07060879139114311</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.7822860491221328</v>
+        <v>0.07060872912177001</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.7822859453398443</v>
+        <v>0.07060862533948152</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7822857723693636</v>
+        <v>0.07060845236900076</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.7822858208010981</v>
+        <v>0.07060850080073532</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7822854610224981</v>
+        <v>0.07060814102213527</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.7822854195095826</v>
+        <v>0.07060809950921987</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7822854748601364</v>
+        <v>0.07060815485977358</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.7822855302106904</v>
+        <v>0.07060821021032752</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.7822855717236057</v>
+        <v>0.07060825172324292</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7822853018896556</v>
+        <v>0.07060798188929283</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.7822853572402095</v>
+        <v>0.07060803723984678</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.7822855025354135</v>
+        <v>0.07060818253505068</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.7822854679413173</v>
+        <v>0.07060814794095442</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.7822854541036787</v>
+        <v>0.07060813410331589</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.7822855440483288</v>
+        <v>0.07060822404796607</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7822858623140135</v>
+        <v>0.07060854231365071</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7822856824247134</v>
+        <v>0.07060836242435058</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7822857239376287</v>
+        <v>0.07060840393726597</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7822855371295095</v>
+        <v>0.07060821712914668</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7822856063177019</v>
+        <v>0.07060828631733916</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7822854056719442</v>
+        <v>0.07060808567158133</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7822854471848596</v>
+        <v>0.07060812718449673</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.998251296146564e-06</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.052178947283033</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7822854748601364</v>
+        <v>0.07060815485977358</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_3_000006.xlsx
+++ b/out/Attention-S4_repeat_3_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.913277624339568</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.913277624339568</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.913277624339568</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.913277624339568</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.124861115779144</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.4174590227899861</v>
+        <v>-0.3364446072187197</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.017459022789986</v>
+        <v>-0.1364446072187196</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.431863202161871</v>
+        <v>-0.1364446072187196</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.017459022789986</v>
+        <v>-0.1364446072187196</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.4174590227899861</v>
+        <v>-0.3364446072187197</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-3.03186320216187</v>
+        <v>-0.3364446072187198</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.4174590227899861</v>
+        <v>-0.3364446072187198</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.4174590227899861</v>
+        <v>-0.3364446072187197</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.124861115779144</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.124861115779144</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.4174590227899861</v>
+        <v>-0.3364446072187197</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002167933316328563</v>
+        <v>-0.0001748393294306006</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2790299051992228</v>
+        <v>0.2250316258433004</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.017459022789986</v>
+        <v>-0.1364446072187196</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.558587869200261</v>
+        <v>0.4504895416536478</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.06443947414094801</v>
+        <v>-0.05196914914268678</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-3.03186320216187</v>
+        <v>-0.9248611157791441</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2143736377266419</v>
+        <v>0.1728876373711832</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.913277624339568</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2143736377266419</v>
+        <v>0.1728876373711832</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.913277624339568</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2143736377266419</v>
+        <v>0.1728876373711832</v>
       </c>
     </row>
     <row r="49">
@@ -39892,17 +39892,17 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.124861115779144</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2143736377266419</v>
+        <v>0.1728583788067563</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>-0.02730000736374358</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.4174590227899861</v>
+        <v>-1.124861115779144</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2142181103627183</v>
+        <v>0.1455583714430127</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2098254224174885</v>
+        <v>0</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-3.03186320216187</v>
+        <v>-0.3364446072187197</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.6344178076558942</v>
+        <v>0.1454690511560643</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1189164494470218</v>
+        <v>0.009265302889873081</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.017459022789986</v>
+        <v>-1.124861115779144</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6621722477533422</v>
+        <v>0.1589641880214547</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.04545446575991044</v>
+        <v>0</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-3.03186320216187</v>
+        <v>-0.1364446072187196</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6339956083353591</v>
+        <v>0.1504254246106131</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.07232407436583781</v>
+        <v>0.1205353711928156</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.017459022789986</v>
+        <v>-0.9248611157791441</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.7332013087964265</v>
+        <v>0.3960673418102187</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04462322612253995</v>
+        <v>0.08121713915928767</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-2.431863202161871</v>
+        <v>-0.1364446072187196</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.7500666126926449</v>
+        <v>0.4378270499041753</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03529366886793676</v>
+        <v>0.07275444909902096</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.017459022789986</v>
+        <v>-0.9248611157791441</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.7760110817772639</v>
+        <v>0.5020674233201677</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01545949057915544</v>
+        <v>0.03095990638325878</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-3.03186320216187</v>
+        <v>-0.9248611157791441</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.7716012733357656</v>
+        <v>0.4911485738905743</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01265231612104198</v>
+        <v>0.02767048456031609</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.124861115779144</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.7814412070586635</v>
+        <v>0.5155146783515003</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.006267748663672829</v>
+        <v>0.01369874382573906</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.4174590227899861</v>
+        <v>-0.3364446072187197</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.7813183675816443</v>
+        <v>0.5152177837261839</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.003670753839263306</v>
+        <v>0.00818040964319601</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7823862616255859</v>
+        <v>0.5178690092834571</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001832876919631653</v>
+        <v>0.004087704821598005</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.7823788710057181</v>
+        <v>0.5178580906882089</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0009025361073440396</v>
+        <v>0.002013122950285518</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.7823498572915786</v>
+        <v>0.5177936385535058</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0005251638152329905</v>
+        <v>0.001191732276910417</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7824971497944204</v>
+        <v>0.5181656799396037</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001678093721583097</v>
+        <v>0.0003678068750133196</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.7823092626698283</v>
+        <v>0.5177073394753919</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>8.19713484444194e-05</v>
+        <v>0.0001828131829031716</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.782305295364584</v>
+        <v>0.5177048880307367</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.375480506233813e-05</v>
+        <v>9.912724557629641e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.7823086581029661</v>
+        <v>0.5177203981839937</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.745641700775619e-05</v>
+        <v>4.610807037515907e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.782302030110225</v>
+        <v>0.517711363281097</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>8.923309997209489e-06</v>
+        <v>2.756129907024117e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.7823029483463702</v>
+        <v>0.517720347558534</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.358871600787948e-06</v>
+        <v>8.038063083497353e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.7822959460555492</v>
+        <v>0.5177110108735687</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.16696438401113e-06</v>
+        <v>2.659266788927341e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7822920839804529</v>
+        <v>0.5177086635781653</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.938917334575396e-06</v>
+        <v>5.622719581563622e-07</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7822875366682678</v>
+        <v>0.5177045689537945</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0</v>
+        <v>-2.12902730447744e-06</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7822876266129177</v>
+        <v>0.5176997447809062</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.7822867686793329</v>
+        <v>0.5176988868473215</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.7822869970003676</v>
+        <v>0.5176991151683561</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.4174590227899861</v>
+        <v>-0.3364446072187197</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.7822862013361559</v>
+        <v>0.5176983195041444</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.124861115779144</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.782286263605529</v>
+        <v>0.5176983817735175</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.913277624339568</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.7822862912808058</v>
+        <v>0.5176984094487943</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.913277624339568</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7822864434948291</v>
+        <v>0.5176985616628176</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.913277624339568</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.7822860975538674</v>
+        <v>0.5176982157218559</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.913277624339568</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.782286173660879</v>
+        <v>0.5176982918288675</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-3.03186320216187</v>
+        <v>-1.124861115779144</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7822863397125406</v>
+        <v>0.5176984578805292</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.4174590227899861</v>
+        <v>-0.3364446072187197</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.7822866994911407</v>
+        <v>0.5176988176591292</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.7822867202475984</v>
+        <v>0.5176988384155868</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.017459022789986</v>
+        <v>-0.1364446072187196</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.7822868240298868</v>
+        <v>0.5176989421978754</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-2.431863202161871</v>
+        <v>-0.1364446072187196</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7822870523509216</v>
+        <v>0.51769917051891</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.017459022789986</v>
+        <v>-0.1364446072187196</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.7822869278121753</v>
+        <v>0.5176990459801638</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.7822869554874522</v>
+        <v>0.5176990736554407</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.7822870108380061</v>
+        <v>0.5176991290059947</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.7822872737531369</v>
+        <v>0.5176993919211254</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.782287190727306</v>
+        <v>0.5176993088952946</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7822869831627293</v>
+        <v>0.5176991013307178</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7822869970003676</v>
+        <v>0.5176991151683561</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7822871353767523</v>
+        <v>0.5176992535447409</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.017459022789986</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7822868517051638</v>
+        <v>0.5176989698731522</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.6519719013417048</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7822866787346829</v>
+        <v>0.5176987969026715</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7822865749523945</v>
+        <v>0.517698693120383</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.7822867202475984</v>
+        <v>0.5176988384155868</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7822869624062716</v>
+        <v>0.5176990805742601</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7822867894357907</v>
+        <v>0.5176989076037791</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.7822864919265636</v>
+        <v>0.5176986100945522</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7822864780889252</v>
+        <v>0.5176985962569136</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7822861113915059</v>
+        <v>0.5176982295594944</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.7822861113915059</v>
+        <v>0.5176982295594944</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.7822860491221328</v>
+        <v>0.5176981672901213</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.7822859453398443</v>
+        <v>0.5176980635078329</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7822857723693636</v>
+        <v>0.517697890537352</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.7822858208010981</v>
+        <v>0.5176979389690867</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7822854610224981</v>
+        <v>0.5176975791904865</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.7822854195095826</v>
+        <v>0.5176975376775712</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7822854748601364</v>
+        <v>0.5176975930281249</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.7822855302106904</v>
+        <v>0.5176976483786788</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.7822855717236057</v>
+        <v>0.5176976898915943</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7822853018896556</v>
+        <v>0.5176974200576442</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.7822853572402095</v>
+        <v>0.5176974754081981</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.7822855025354135</v>
+        <v>0.517697620703402</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.7822854679413173</v>
+        <v>0.5176975861093057</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.7822854541036787</v>
+        <v>0.5176975722716672</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.7822855440483288</v>
+        <v>0.5176976622163174</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7822858623140135</v>
+        <v>0.517697980482002</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7822856824247134</v>
+        <v>0.5176978005927019</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7822857239376287</v>
+        <v>0.5176978421056173</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7822855371295095</v>
+        <v>0.517697655297498</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7822856063177019</v>
+        <v>0.5176977244856905</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.4174590227899861</v>
+        <v>0.4519719013417047</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7822854056719442</v>
+        <v>0.5176975238399326</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.4174590227899861</v>
+        <v>-0.3364446072187197</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7822854471848596</v>
+        <v>0.5176975653528481</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.998251296146564e-06</v>
+        <v>-4.278197982492988e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-3.03186320216187</v>
+        <v>-0.7306528614989318</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7822854748601364</v>
+        <v>0.5176975930281249</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_3_000006.xlsx
+++ b/out/Attention-S4_repeat_3_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.003507945686578751</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.913277624339568</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.002167254686355591</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.913277624339568</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.002083037048578262</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.913277624339568</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.001143798232078552</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.913277624339568</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.0004498064517974854</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.124861115779144</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.0008726567029953003</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3364446072187197</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.0002855323255062103</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.001118931919336319</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.6519719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.0006529577076435089</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.1364446072187196</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-4.072859883308411e-05</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.1364446072187196</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.001383371651172638</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.1364446072187196</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.002163078635931015</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.6519719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.00355856865644455</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.6519719013417048</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.00293513759970665</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.6519719013417048</v>
+        <v>0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.001910462975502014</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.6519719013417048</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.002840094268321991</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.6519719013417048</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.004359904676675797</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.6519719013417048</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.005523070693016052</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.6519719013417048</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.006005778908729553</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.6519719013417048</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.003777544945478439</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.6519719013417048</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.004183992743492126</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.005435924977064133</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.005382377654314041</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.005278032273054123</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.00433427095413208</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.00567333772778511</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.008377891033887863</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.00382721796631813</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.003956981003284454</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.002738151699304581</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.000547848641872406</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.0008007325232028961</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.000844951719045639</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.001353304833173752</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3364446072187197</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.000105883926153183</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3364446072187198</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>4.764273762702942e-05</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3364446072187198</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>5.93923032283783e-05</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3364446072187197</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.0006579384207725525</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.124861115779144</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.0001863017678260803</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.124861115779144</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.000143151730298996</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3364446072187197</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.001469820737838745</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.003216341137886047</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.6519719013417048</v>
+        <v>0.3</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.009768947958946228</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.6519719013417048</v>
+        <v>0.3</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001748393294306006</v>
+        <v>-0.0001344367990464671</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2250316258433004</v>
+        <v>0.1730306324954369</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.00775330513715744</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.1364446072187196</v>
+        <v>0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4504895416536478</v>
+        <v>0.3463887221801225</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.05196914914268678</v>
+        <v>-0.03995988516112875</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.001347053796052933</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.9248611157791441</v>
+        <v>0.16</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1728876373711832</v>
+        <v>0.1329363105352616</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.001125693321228027</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.913277624339568</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1728876373711832</v>
+        <v>0.1329363105352616</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.001664489507675171</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.913277624339568</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1728876373711832</v>
+        <v>0.1329184927685836</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.05473987040240787</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.00401199609041214</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.124861115779144</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.1728583788067563</v>
+        <v>0.242507558634111</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>-0.02730000736374358</v>
+        <v>0.01047385741160038</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.0009226053953170776</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.124861115779144</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.1455583714430127</v>
+        <v>0.208635320281073</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.01834617211370855</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.001680232584476471</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3364446072187197</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.1454690511560643</v>
+        <v>0.2348588171686423</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.009265302889873081</v>
+        <v>0.01004571929095453</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.001166161149740219</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.124861115779144</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.1589641880214547</v>
+        <v>0.2365895825316326</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.004146151647240354</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.003092549741268158</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.1364446072187196</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.1504254246106131</v>
+        <v>0.2348277405984774</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1205353711928156</v>
+        <v>0.005166729150709232</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.008156038820743561</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9248611157791441</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.3960673418102187</v>
+        <v>0.2410156044420945</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.08121713915928767</v>
+        <v>0.00310844112183113</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.001010723412036896</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.1364446072187196</v>
+        <v>0.16</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.4378270499041753</v>
+        <v>0.2420641331890666</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.07275444909902096</v>
+        <v>0.002362928770734772</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.01804270967841148</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9248611157791441</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5020674233201677</v>
+        <v>0.2436793036524139</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.03095990638325878</v>
+        <v>0.001042343471205433</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.009385548532009125</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9248611157791441</v>
+        <v>0.16</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4911485738905743</v>
+        <v>0.243399391580068</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.02767048456031609</v>
+        <v>0.0008248076865604839</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.004335124045610428</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.124861115779144</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5155146783515003</v>
+        <v>0.2440088856121087</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.01369874382573906</v>
+        <v>0.0004077442434453328</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.03557915985584259</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3364446072187197</v>
+        <v>0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5152177837261839</v>
+        <v>0.2439965191517479</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.00818040964319601</v>
+        <v>0.0002335544611416224</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.03407883271574974</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.6519719013417048</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5178690092834571</v>
+        <v>0.2440585768405697</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.004087704821598005</v>
+        <v>0.0001142772305708112</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.0166616328060627</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.6519719013417048</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5178580906882089</v>
+        <v>0.2440534283323658</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.002013122950285518</v>
+        <v>5.536761141001575e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.01786065474152565</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.6519719013417048</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5177936385535058</v>
+        <v>0.2440469001869205</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.001191732276910417</v>
+        <v>2.837652777902737e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.02740334905683994</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.6519719013417048</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5181656799396037</v>
+        <v>0.2440515935964664</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0003678068750133196</v>
+        <v>6.159850569859539e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.01549408584833145</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.6519719013417048</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5177073394753919</v>
+        <v>0.244034402432126</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001828131829031716</v>
+        <v>1.73737344181313e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.008393146097660065</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.6519719013417048</v>
+        <v>-0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5177048880307367</v>
+        <v>0.2440294769826468</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>9.912724557629641e-05</v>
+        <v>-2.553803869891494e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.003605406731367111</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.6519719013417048</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5177203981839937</v>
+        <v>0.2440250758540418</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>4.610807037515907e-05</v>
+        <v>-2.629819553036738e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.01058415696024895</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.6519719013417048</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.517711363281097</v>
+        <v>0.244019920665469</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>2.756129907024117e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.01937780901789665</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.6519719013417048</v>
+        <v>-0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.517720347558534</v>
+        <v>0.2440204603333692</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>8.038063083497353e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.01266179233789444</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5177110108735687</v>
+        <v>0.244020128230046</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>2.659266788927341e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.01877768710255623</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5177086635781653</v>
+        <v>0.2440205087651038</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>5.622719581563622e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.01145116612315178</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5177045689537945</v>
+        <v>0.2440207370861384</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-2.12902730447744e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.01116100326180458</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5176997447809062</v>
+        <v>0.2440208270307884</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.001283083111047745</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.16</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5176988868473215</v>
+        <v>0.2440199690972036</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.007305353879928589</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5176991151683561</v>
+        <v>0.2440201974182383</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.000643901526927948</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3364446072187197</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5176983195041444</v>
+        <v>0.2440194017540265</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.006923895329236984</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.124861115779144</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5176983817735175</v>
+        <v>0.2440194640233996</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.001725967973470688</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.913277624339568</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5176984094487943</v>
+        <v>0.2440194916986765</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.005566287785768509</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.913277624339568</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5176985616628176</v>
+        <v>0.2440196439126998</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.006557632237672806</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.913277624339568</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5176982157218559</v>
+        <v>0.244019297971738</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.003518007695674896</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.913277624339568</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5176982918288675</v>
+        <v>0.2440193740787497</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.00319049134850502</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.124861115779144</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5176984578805292</v>
+        <v>0.2440195401304113</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.001514073461294174</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3364446072187197</v>
+        <v>0.16</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5176988176591292</v>
+        <v>0.2440198999090113</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.007828392088413239</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.6519719013417048</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5176988384155868</v>
+        <v>0.244019920665469</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.009460147470235825</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.1364446072187196</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5176989421978754</v>
+        <v>0.2440200244477575</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.0004240162670612335</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.1364446072187196</v>
+        <v>0.16</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.51769917051891</v>
+        <v>0.2440202527687922</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.0005405955016613007</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.1364446072187196</v>
+        <v>0.16</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5176990459801638</v>
+        <v>0.244020128230046</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.0004207305610179901</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.6519719013417048</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5176990736554407</v>
+        <v>0.2440201559053229</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.008046753704547882</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.6519719013417048</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5176991290059947</v>
+        <v>0.2440202112558768</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.003206450492143631</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.6519719013417048</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5176993919211254</v>
+        <v>0.2440204741710075</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.002778016030788422</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.6519719013417048</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5176993088952946</v>
+        <v>0.2440203911451767</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.001773923635482788</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.6519719013417048</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5176991013307178</v>
+        <v>0.2440201835806</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.007226832211017609</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.6519719013417048</v>
+        <v>0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5176991151683561</v>
+        <v>0.2440201974182383</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.007505033165216446</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.6519719013417048</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5176992535447409</v>
+        <v>0.244020335794623</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.004892926663160324</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.6519719013417048</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5176989698731522</v>
+        <v>0.2440200521230344</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.00668657198548317</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.6519719013417048</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5176987969026715</v>
+        <v>0.2440198791525536</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.009145814925432205</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.517698693120383</v>
+        <v>0.2440197753702651</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.002652972936630249</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5176988384155868</v>
+        <v>0.244019920665469</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.003884714096784592</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5176990805742601</v>
+        <v>0.2440201628241423</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.008866570889949799</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5176989076037791</v>
+        <v>0.2440199898536613</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.003907844424247742</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5176986100945522</v>
+        <v>0.2440196923444343</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.008024487644433975</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5176985962569136</v>
+        <v>0.2440196785067958</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.006302662193775177</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5176982295594944</v>
+        <v>0.2440193118093766</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.00618816539645195</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5176982295594944</v>
+        <v>0.2440193118093766</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.009554360061883926</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5176981672901213</v>
+        <v>0.2440192495400035</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.002249442040920258</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5176980635078329</v>
+        <v>0.244019145757715</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.003173358738422394</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.517697890537352</v>
+        <v>0.2440189727872342</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.00284624844789505</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5176979389690867</v>
+        <v>0.2440190212189688</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.00164785236120224</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5176975791904865</v>
+        <v>0.2440186614403687</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.002966031432151794</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5176975376775712</v>
+        <v>0.2440186199274534</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.004975061863660812</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5176975930281249</v>
+        <v>0.2440186752780071</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.002369549125432968</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5176976483786788</v>
+        <v>0.244018730628561</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.003677554428577423</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5176976898915943</v>
+        <v>0.2440187721414764</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.003482989966869354</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5176974200576442</v>
+        <v>0.2440185023075263</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.004165302962064743</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5176974754081981</v>
+        <v>0.2440185576580803</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.00479457899928093</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.517697620703402</v>
+        <v>0.2440187029532842</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.004526924341917038</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5176975861093057</v>
+        <v>0.2440186683591879</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.004480868577957153</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5176975722716672</v>
+        <v>0.2440186545215494</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.006830316036939621</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5176976622163174</v>
+        <v>0.2440187444661995</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.01592665538191795</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.517697980482002</v>
+        <v>0.2440190627318842</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.004273656755685806</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.4519719013417047</v>
+        <v>0.16</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5176978005927019</v>
+        <v>0.2440188828425841</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.003411367535591125</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5176978421056173</v>
+        <v>0.2440189243554994</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.001395124942064285</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.517697655297498</v>
+        <v>0.2440187375473802</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.001343805342912674</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5176977244856905</v>
+        <v>0.2440188067355726</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.00282716378569603</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.4519719013417047</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5176975238399326</v>
+        <v>0.2440186060898148</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.001354202628135681</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3364446072187197</v>
+        <v>-0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5176975653528481</v>
+        <v>0.2440186476027302</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-4.278197982492988e-06</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.001142174005508423</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7306528614989318</v>
+        <v>-0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5176975930281249</v>
+        <v>0.2440186752780071</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_3_000006.xlsx
+++ b/out/Attention-S4_repeat_3_000006.xlsx
@@ -65339,7 +65339,7 @@
         <v>-0.00319049134850502</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0.2440195401304113</v>
@@ -66134,7 +66134,7 @@
         <v>0.001514073461294174</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.16</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
         <v>0.2440198999090113</v>
@@ -66929,7 +66929,7 @@
         <v>0.007828392088413239</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.1600000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
         <v>0.244019920665469</v>
@@ -67724,7 +67724,7 @@
         <v>0.009460147470235825</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.1600000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
         <v>0.2440200244477575</v>
@@ -68519,7 +68519,7 @@
         <v>-0.0004240162670612335</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.16</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0.2440202527687922</v>
@@ -69314,7 +69314,7 @@
         <v>0.0005405955016613007</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.16</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
         <v>0.244020128230046</v>
@@ -70109,7 +70109,7 @@
         <v>0.0004207305610179901</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC87" t="n">
         <v>0.2440201559053229</v>
@@ -70904,7 +70904,7 @@
         <v>0.008046753704547882</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
         <v>0.2440202112558768</v>
@@ -71699,7 +71699,7 @@
         <v>0.003206450492143631</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
         <v>0.2440204741710075</v>
@@ -72494,7 +72494,7 @@
         <v>0.002778016030788422</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0.2440203911451767</v>
@@ -73289,7 +73289,7 @@
         <v>0.001773923635482788</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5799999999999998</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC91" t="n">
         <v>0.2440201835806</v>
@@ -79649,7 +79649,7 @@
         <v>0.008866570889949799</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="JC99" t="n">
         <v>0.2440199898536613</v>
